--- a/data/excel/camiones_puertos_mensual.xlsx
+++ b/data/excel/camiones_puertos_mensual.xlsx
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19T21:01:37Z</t>
+          <t>2026-10-20T18:08:31Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/camiones_puertos_mensual.xlsx
+++ b/data/excel/camiones_puertos_mensual.xlsx
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T18:08:31Z</t>
+          <t>2026-10-21T18:44:48Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/camiones_puertos_mensual.xlsx
+++ b/data/excel/camiones_puertos_mensual.xlsx
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21T18:44:48Z</t>
+          <t>2026-10-23T05:23:48Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/camiones_puertos_mensual.xlsx
+++ b/data/excel/camiones_puertos_mensual.xlsx
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23T05:23:48Z</t>
+          <t>2026-10-24T05:02:43Z</t>
         </is>
       </c>
     </row>
